--- a/assets/constructions/examples/ctd_burr.xlsx
+++ b/assets/constructions/examples/ctd_burr.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AN6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -604,32 +604,57 @@
           <t>zefp</t>
         </is>
       </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>302008/4STx300</t>
+          <t>M41389</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CERIN</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>30-STx300</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -640,18 +665,20 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>20</v>
+        <v>12.7</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>25</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
+        <v>25.4</v>
+      </c>
+      <c r="O2" t="n">
+        <v>25.4</v>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>HA-8</t>
+          <t>HA-6.35</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -660,39 +687,27 @@
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>HM CK 30 M Medium</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>HM CK 30 M Medium</t>
-        </is>
-      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>WN</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>8</v>
+        <v>6.35</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>325</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
@@ -703,7 +718,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2021/Rotary burs_catalogue.pdf</t>
+          <t>2017/_widia-FullCatalogue.pdf</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -718,12 +733,23 @@
       </c>
       <c r="AI2" t="n">
         <v>1</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2253/2</t>
+          <t>341608/3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -733,42 +759,40 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>G</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>3</v>
       </c>
-      <c r="H3" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="b">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>HA-2.35</t>
+          <t>HA-8</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -801,15 +825,15 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.35</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
@@ -836,11 +860,22 @@
       <c r="AI3" t="n">
         <v>1</v>
       </c>
+      <c r="AJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4863/4</t>
+          <t>301006/3x150</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -850,40 +885,40 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>30-x150</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>5.4</v>
+        <v>20</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>HA-3</t>
+          <t>HA-6</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -909,22 +944,22 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>DIN 8033</t>
+          <t>WN</t>
         </is>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>40.4</v>
+        <v>170</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
@@ -951,11 +986,22 @@
       <c r="AI4" t="n">
         <v>1</v>
       </c>
+      <c r="AJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>321606/6x100</t>
+          <t>311606/5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -965,26 +1011,26 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32-x100</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PMKNS</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>16</v>
@@ -993,7 +1039,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1024,7 +1070,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>WN</t>
+          <t>DIN 8033</t>
         </is>
       </c>
       <c r="W5" t="n">
@@ -1039,7 +1085,7 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
@@ -1066,11 +1112,22 @@
       <c r="AI5" t="n">
         <v>1</v>
       </c>
+      <c r="AJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>341006/4x300</t>
+          <t>4853/3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1080,40 +1137,40 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>34-x300</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>HA-6</t>
+          <t>HA-3</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1139,22 +1196,22 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>WN</t>
+          <t>DIN 8033</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>320</v>
+        <v>39.5</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
@@ -1181,6 +1238,17 @@
       <c r="AI6" t="n">
         <v>1</v>
       </c>
+      <c r="AJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
